--- a/06_Debt_Finance/_template_CREDIT.xlsx
+++ b/06_Debt_Finance/_template_CREDIT.xlsx
@@ -8,18 +8,25 @@
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Assumptions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Capital Structure" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Maturity Ladder" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Refinancing" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Interest Rate Risk" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Covenants" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Recovery" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Checks" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Sources" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="RefreshLog" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Institutional Surface" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Challenge Log" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Lineage Map" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Assumptions" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Capital Structure" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Maturity Ladder" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Refinancing" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Interest Rate Risk" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Covenants" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Recovery" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Checks" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Sources" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="RefreshLog" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="FS_MODEL_ID">'Institutional Surface'!$C$4</definedName>
+    <definedName name="FS_DOMAIN">'Institutional Surface'!$C$5</definedName>
+    <definedName name="FS_MATURITY">'Institutional Surface'!$C$6</definedName>
+  </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
 </file>
@@ -33,7 +40,7 @@
     <numFmt numFmtId="167" formatCode="0.00%;[Red](0.00%);-"/>
     <numFmt numFmtId="168" formatCode="0 &quot;bps&quot;"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -86,8 +93,20 @@
       <color rgb="00008000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -104,8 +123,18 @@
         <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0017365D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAF7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -123,11 +152,16 @@
         <color rgb="00111827"/>
       </top>
     </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00B7B7B7"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -160,6 +194,15 @@
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -729,6 +772,447 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Covenant &amp; Rating Screens</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>Threshold</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>Headroom / status</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Gross leverage</t>
+        </is>
+      </c>
+      <c r="C5" s="21">
+        <f>'Capital Structure'!C13</f>
+        <v/>
+      </c>
+      <c r="D5" s="21">
+        <f>Assumptions!E18</f>
+        <v/>
+      </c>
+      <c r="E5" s="21">
+        <f>D5-C5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Interest coverage</t>
+        </is>
+      </c>
+      <c r="C6" s="21">
+        <f>'Capital Structure'!C15</f>
+        <v/>
+      </c>
+      <c r="D6" s="21">
+        <f>Assumptions!E19</f>
+        <v/>
+      </c>
+      <c r="E6" s="21">
+        <f>C6-D6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Near-term maturities / debt</t>
+        </is>
+      </c>
+      <c r="C7" s="16">
+        <f>IFERROR(SUM('Maturity Ladder'!C10:E10)/'Capital Structure'!C10,0)</f>
+        <v/>
+      </c>
+      <c r="D7" s="16" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E7" s="16">
+        <f>D7-C7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Refinancing status</t>
+        </is>
+      </c>
+      <c r="C8">
+        <f>Refinancing!G8</f>
+        <v/>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E8">
+        <f>IF(C8=D8,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:E2"/>
+  </mergeCells>
+  <conditionalFormatting sqref="E8">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>E8="PASS"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="1">
+      <formula>E8="FAIL"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="2">
+      <formula>E8="REVIEW"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="1">
+      <formula>E8="BREACH"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:E13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Claim Recovery Waterfall</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>Downside</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Stressed EBITDA</t>
+        </is>
+      </c>
+      <c r="C5" s="15">
+        <f>Assumptions!C5</f>
+        <v/>
+      </c>
+      <c r="D5" s="15">
+        <f>Assumptions!D5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Recovery multiple</t>
+        </is>
+      </c>
+      <c r="C6" s="21">
+        <f>Assumptions!C20</f>
+        <v/>
+      </c>
+      <c r="D6" s="21">
+        <f>Assumptions!D20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Enterprise value</t>
+        </is>
+      </c>
+      <c r="C7" s="15">
+        <f>C5*C6</f>
+        <v/>
+      </c>
+      <c r="D7" s="15">
+        <f>D5*D6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>EV haircut</t>
+        </is>
+      </c>
+      <c r="C8" s="15">
+        <f>C7*Assumptions!C21</f>
+        <v/>
+      </c>
+      <c r="D8" s="15">
+        <f>D7*Assumptions!D21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Distributable value</t>
+        </is>
+      </c>
+      <c r="C9" s="15">
+        <f>C7-C8</f>
+        <v/>
+      </c>
+      <c r="D9" s="15">
+        <f>D7-D8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Gross debt</t>
+        </is>
+      </c>
+      <c r="C10" s="15">
+        <f>'Capital Structure'!C10</f>
+        <v/>
+      </c>
+      <c r="D10" s="15">
+        <f>'Capital Structure'!C10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Recovery value</t>
+        </is>
+      </c>
+      <c r="C11" s="15">
+        <f>MIN(C9,C10)</f>
+        <v/>
+      </c>
+      <c r="D11" s="15">
+        <f>MIN(D9,D10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Recovery rate</t>
+        </is>
+      </c>
+      <c r="C12" s="16">
+        <f>IFERROR(C11/C10,0)</f>
+        <v/>
+      </c>
+      <c r="D12" s="16">
+        <f>IFERROR(D11/D10,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>LGD</t>
+        </is>
+      </c>
+      <c r="C13" s="16">
+        <f>1-C12</f>
+        <v/>
+      </c>
+      <c r="D13" s="16">
+        <f>1-D12</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:E2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:C9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Model Checks</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Sources equal uses</t>
+        </is>
+      </c>
+      <c r="C5">
+        <f>IF(Refinancing!G8="PASS","PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Debt nonnegative</t>
+        </is>
+      </c>
+      <c r="C6">
+        <f>IF('Capital Structure'!C10&gt;=0,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Maturities reconcile</t>
+        </is>
+      </c>
+      <c r="C7">
+        <f>IF(ABS(SUM('Maturity Ladder'!C10:H10)-'Capital Structure'!C10)&lt;0.01,"PASS","REVIEW")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Recovery bounded</t>
+        </is>
+      </c>
+      <c r="C8">
+        <f>IF(AND(MIN(Recovery!C12:D12)&gt;=0,MAX(Recovery!C12:D12)&lt;=1),"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="C9">
+        <f>IF(COUNTIF(C5:C8,"FAIL")+COUNTIF(C5:C8,"REVIEW")=0,"PASS","REVIEW")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:C2"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C5:C9">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>C5="PASS"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="1">
+      <formula>C5="FAIL"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="2">
+      <formula>C5="REVIEW"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="1">
+      <formula>C5="BREACH"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:E8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="58" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
@@ -860,7 +1344,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1131,6 +1615,1318 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="B2:F63"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="26" t="inlineStr">
+        <is>
+          <t>Debt Finance — Institutional Decision Surface</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="27" t="inlineStr">
+        <is>
+          <t>Model ID</t>
+        </is>
+      </c>
+      <c r="C4" s="28" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="27" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C5" s="28" t="inlineStr">
+        <is>
+          <t>Debt Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="27" t="inlineStr">
+        <is>
+          <t>Declared maturity</t>
+        </is>
+      </c>
+      <c r="C6" s="28" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="27" t="inlineStr">
+        <is>
+          <t>Canonical builder</t>
+        </is>
+      </c>
+      <c r="C7" s="28" t="inlineStr">
+        <is>
+          <t>tools/builders/build_debt_finance_template.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="27" t="inlineStr">
+        <is>
+          <t>Decision arena</t>
+        </is>
+      </c>
+      <c r="C8" s="28" t="inlineStr">
+        <is>
+          <t>issuer treasury, syndicate desk, rating agencies and board finance committee</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="27" t="inlineStr">
+        <is>
+          <t>Committee artifact</t>
+        </is>
+      </c>
+      <c r="C9" s="28" t="inlineStr">
+        <is>
+          <t>financing alternatives and execution memo</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="27" t="inlineStr">
+        <is>
+          <t>Operating cadence</t>
+        </is>
+      </c>
+      <c r="C10" s="28" t="inlineStr">
+        <is>
+          <t>daily during execution; monthly treasury</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="29" t="inlineStr">
+        <is>
+          <t>Key decision outputs</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="30" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C13" s="30" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="D13" s="30" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="E13" s="30" t="inlineStr">
+        <is>
+          <t>Evidence / location</t>
+        </is>
+      </c>
+      <c r="F13" s="30" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>all-in cost and break-even</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>maturity and refinancing profile</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ratings and covenant capacity</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>4</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>base, downside and break-even outputs</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>5</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>liquidity / funding requirement and binding constraint</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="29" t="inlineStr">
+        <is>
+          <t>Insider questions</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C21" s="30" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="D21" s="30" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="E21" s="30" t="inlineStr">
+        <is>
+          <t>Evidence / location</t>
+        </is>
+      </c>
+      <c r="F21" s="30" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Where is the break-even between fixed and floating?</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>2</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>What flex can arrangers exercise?</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>3</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Which maturities cluster under the downside?</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>4</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Which assumption is owner-approved versus modeler judgement?</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="n">
+        <v>5</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>What fails first and who must act?</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="29" t="inlineStr">
+        <is>
+          <t>Scenario families</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="30" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C29" s="30" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="D29" s="30" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="E29" s="30" t="inlineStr">
+        <is>
+          <t>Evidence / location</t>
+        </is>
+      </c>
+      <c r="F29" s="30" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>base-rate and spread widening</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="n">
+        <v>2</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>failed syndication / flex</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="n">
+        <v>3</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ratings downgrade</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="n">
+        <v>4</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>data freshness / source failure</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="n">
+        <v>5</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>combined severe-but-plausible downside</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="29" t="inlineStr">
+        <is>
+          <t>Primary diligence documents</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="30" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C37" s="30" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="D37" s="30" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="E37" s="30" t="inlineStr">
+        <is>
+          <t>Evidence / location</t>
+        </is>
+      </c>
+      <c r="F37" s="30" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>bank proposals and commitment letters</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="n">
+        <v>2</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>indentures / credit agreements</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="n">
+        <v>3</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>rating-agency feedback</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="n">
+        <v>4</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>approved model card and assumption register</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="n">
+        <v>5</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>independent validation and challenge record</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="29" t="inlineStr">
+        <is>
+          <t>Challenge tests</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="30" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C45" s="30" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="D45" s="30" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="E45" s="30" t="inlineStr">
+        <is>
+          <t>Evidence / location</t>
+        </is>
+      </c>
+      <c r="F45" s="30" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>sources and uses balance</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="n">
+        <v>2</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>all-in yield includes fees and OID</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="n">
+        <v>3</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>maturity ladder equals debt ledger</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="n">
+        <v>4</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>source-to-model lineage is reproducible</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="n">
+        <v>5</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>units, signs, dates and legal definitions reconcile</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="29" t="inlineStr">
+        <is>
+          <t>Known failure modes</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="30" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C53" s="30" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="D53" s="30" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="E53" s="30" t="inlineStr">
+        <is>
+          <t>Evidence / location</t>
+        </is>
+      </c>
+      <c r="F53" s="30" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>quoting coupon instead of all-in cost</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="n">
+        <v>2</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>missing ticking fees and flex</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="n">
+        <v>3</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>assuming refinancing proceeds before conditions</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="n">
+        <v>4</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>stale vintage presented as current</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="n">
+        <v>5</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>decision output disconnected from a binding constraint</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="29" t="inlineStr">
+        <is>
+          <t>Regulatory / methodological anchors</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="30" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="C61" s="30" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="D61" s="30" t="inlineStr">
+        <is>
+          <t>Source URL</t>
+        </is>
+      </c>
+      <c r="E61" s="30" t="inlineStr">
+        <is>
+          <t>Applicability</t>
+        </is>
+      </c>
+      <c r="F61" s="30" t="inlineStr">
+        <is>
+          <t>Review note</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Federal Reserve SR 26-2 Model Risk Management</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>governance, validation, change control, monitoring</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>https://www.federalreserve.gov/supervisionreg/srletters/SR2602.htm</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Map explicitly</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Basel SRP31 IRRBB</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>EVE/NII, basis and option risk</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>https://www.bis.org/basel_framework/chapter/SRP/31.htm</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Map explicitly</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="B44:F44"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="B60:F60"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="B52:F52"/>
+  </mergeCells>
+  <dataValidations count="6">
+    <dataValidation sqref="F14:F18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"OPEN,IN REVIEW,CLOSED,NOT APPLICABLE"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F22:F26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"OPEN,IN REVIEW,CLOSED,NOT APPLICABLE"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F30:F34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"OPEN,IN REVIEW,CLOSED,NOT APPLICABLE"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F38:F42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"OPEN,IN REVIEW,CLOSED,NOT APPLICABLE"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F46:F50" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"OPEN,IN REVIEW,CLOSED,NOT APPLICABLE"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F54:F58" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"OPEN,IN REVIEW,CLOSED,NOT APPLICABLE"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:I9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="26" t="inlineStr">
+        <is>
+          <t>Independent Challenge, Override and Closure Log</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="30" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C4" s="30" t="inlineStr">
+        <is>
+          <t>Reviewer</t>
+        </is>
+      </c>
+      <c r="D4" s="30" t="inlineStr">
+        <is>
+          <t>Challenge</t>
+        </is>
+      </c>
+      <c r="E4" s="30" t="inlineStr">
+        <is>
+          <t>Owner response</t>
+        </is>
+      </c>
+      <c r="F4" s="30" t="inlineStr">
+        <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+      <c r="G4" s="30" t="inlineStr">
+        <is>
+          <t>Impact</t>
+        </is>
+      </c>
+      <c r="H4" s="30" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="I4" s="30" t="inlineStr">
+        <is>
+          <t>Closure</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>sources and uses balance</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>all-in yield includes fees and OID</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>maturity ladder equals debt ledger</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>source-to-model lineage is reproducible</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>units, signs, dates and legal definitions reconcile</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:I2"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation sqref="H5:H54" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"OPEN,IN REVIEW,REMEDIATED,ACCEPTED RISK,CLOSED"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G5:G54" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"LOW,MEDIUM,HIGH,CRITICAL"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:J8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="26" t="inlineStr">
+        <is>
+          <t>Source, Transformation, Ownership and Refresh Map</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="30" t="inlineStr">
+        <is>
+          <t>Source class</t>
+        </is>
+      </c>
+      <c r="C4" s="30" t="inlineStr">
+        <is>
+          <t>Cadence</t>
+        </is>
+      </c>
+      <c r="D4" s="30" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="E4" s="30" t="inlineStr">
+        <is>
+          <t>System / provider</t>
+        </is>
+      </c>
+      <c r="F4" s="30" t="inlineStr">
+        <is>
+          <t>As-of</t>
+        </is>
+      </c>
+      <c r="G4" s="30" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="H4" s="30" t="inlineStr">
+        <is>
+          <t>Transform</t>
+        </is>
+      </c>
+      <c r="I4" s="30" t="inlineStr">
+        <is>
+          <t>Downstream</t>
+        </is>
+      </c>
+      <c r="J4" s="30" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>debt ledger</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>daily/weekly</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>principal and legal-entity reconciliation</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>TO MAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>curves and spreads</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>timestamped executable levels</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>TO MAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>model governance evidence</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>per release</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>version, reviewer, sign-off and change log</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>TO MAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>decision-use snapshot</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>per decision</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>immutable as-of date and source receipt</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>TO MAP</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:J2"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="J5:J40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"TO MAP,ACTIVE,STALE,EXCEPTION,RETIRED"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="B2:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1473,7 +3269,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1720,7 +3516,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1953,7 +3749,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2153,7 +3949,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2343,445 +4139,4 @@
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="B2:E8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="2" ht="28" customHeight="1">
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>Covenant &amp; Rating Screens</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>Actual</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>Threshold</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>Headroom / status</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Gross leverage</t>
-        </is>
-      </c>
-      <c r="C5" s="21">
-        <f>'Capital Structure'!C13</f>
-        <v/>
-      </c>
-      <c r="D5" s="21">
-        <f>Assumptions!E18</f>
-        <v/>
-      </c>
-      <c r="E5" s="21">
-        <f>D5-C5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Interest coverage</t>
-        </is>
-      </c>
-      <c r="C6" s="21">
-        <f>'Capital Structure'!C15</f>
-        <v/>
-      </c>
-      <c r="D6" s="21">
-        <f>Assumptions!E19</f>
-        <v/>
-      </c>
-      <c r="E6" s="21">
-        <f>C6-D6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Near-term maturities / debt</t>
-        </is>
-      </c>
-      <c r="C7" s="16">
-        <f>IFERROR(SUM('Maturity Ladder'!C10:E10)/'Capital Structure'!C10,0)</f>
-        <v/>
-      </c>
-      <c r="D7" s="16" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E7" s="16">
-        <f>D7-C7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Refinancing status</t>
-        </is>
-      </c>
-      <c r="C8">
-        <f>Refinancing!G8</f>
-        <v/>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E8">
-        <f>IF(C8=D8,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B2:E2"/>
-  </mergeCells>
-  <conditionalFormatting sqref="E8">
-    <cfRule type="expression" priority="1" dxfId="0">
-      <formula>E8="PASS"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="2" dxfId="1">
-      <formula>E8="FAIL"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="3" dxfId="2">
-      <formula>E8="REVIEW"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="4" dxfId="1">
-      <formula>E8="BREACH"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="B2:E13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="2" ht="28" customHeight="1">
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>Claim Recovery Waterfall</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>Downside</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Stressed EBITDA</t>
-        </is>
-      </c>
-      <c r="C5" s="15">
-        <f>Assumptions!C5</f>
-        <v/>
-      </c>
-      <c r="D5" s="15">
-        <f>Assumptions!D5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Recovery multiple</t>
-        </is>
-      </c>
-      <c r="C6" s="21">
-        <f>Assumptions!C20</f>
-        <v/>
-      </c>
-      <c r="D6" s="21">
-        <f>Assumptions!D20</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Enterprise value</t>
-        </is>
-      </c>
-      <c r="C7" s="15">
-        <f>C5*C6</f>
-        <v/>
-      </c>
-      <c r="D7" s="15">
-        <f>D5*D6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>EV haircut</t>
-        </is>
-      </c>
-      <c r="C8" s="15">
-        <f>C7*Assumptions!C21</f>
-        <v/>
-      </c>
-      <c r="D8" s="15">
-        <f>D7*Assumptions!D21</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Distributable value</t>
-        </is>
-      </c>
-      <c r="C9" s="15">
-        <f>C7-C8</f>
-        <v/>
-      </c>
-      <c r="D9" s="15">
-        <f>D7-D8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Gross debt</t>
-        </is>
-      </c>
-      <c r="C10" s="15">
-        <f>'Capital Structure'!C10</f>
-        <v/>
-      </c>
-      <c r="D10" s="15">
-        <f>'Capital Structure'!C10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Recovery value</t>
-        </is>
-      </c>
-      <c r="C11" s="15">
-        <f>MIN(C9,C10)</f>
-        <v/>
-      </c>
-      <c r="D11" s="15">
-        <f>MIN(D9,D10)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Recovery rate</t>
-        </is>
-      </c>
-      <c r="C12" s="16">
-        <f>IFERROR(C11/C10,0)</f>
-        <v/>
-      </c>
-      <c r="D12" s="16">
-        <f>IFERROR(D11/D10,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>LGD</t>
-        </is>
-      </c>
-      <c r="C13" s="16">
-        <f>1-C12</f>
-        <v/>
-      </c>
-      <c r="D13" s="16">
-        <f>1-D12</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B2:E2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="B2:C9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="2" ht="28" customHeight="1">
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>Model Checks</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>Check</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Sources equal uses</t>
-        </is>
-      </c>
-      <c r="C5">
-        <f>IF(Refinancing!G8="PASS","PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Debt nonnegative</t>
-        </is>
-      </c>
-      <c r="C6">
-        <f>IF('Capital Structure'!C10&gt;=0,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Maturities reconcile</t>
-        </is>
-      </c>
-      <c r="C7">
-        <f>IF(ABS(SUM('Maturity Ladder'!C10:H10)-'Capital Structure'!C10)&lt;0.01,"PASS","REVIEW")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Recovery bounded</t>
-        </is>
-      </c>
-      <c r="C8">
-        <f>IF(AND(MIN(Recovery!C12:D12)&gt;=0,MAX(Recovery!C12:D12)&lt;=1),"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="C9">
-        <f>IF(COUNTIF(C5:C8,"FAIL")+COUNTIF(C5:C8,"REVIEW")=0,"PASS","REVIEW")</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B2:C2"/>
-  </mergeCells>
-  <conditionalFormatting sqref="C5:C9">
-    <cfRule type="expression" priority="1" dxfId="0">
-      <formula>C5="PASS"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="2" dxfId="1">
-      <formula>C5="FAIL"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="3" dxfId="2">
-      <formula>C5="REVIEW"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="4" dxfId="1">
-      <formula>C5="BREACH"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/06_Debt_Finance/_template_CREDIT.xlsx
+++ b/06_Debt_Finance/_template_CREDIT.xlsx
@@ -1164,7 +1164,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:C9"/>
+  <dimension ref="B2:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1238,11 +1238,22 @@
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
+          <t>Refinancing funded without equity plug</t>
+        </is>
+      </c>
+      <c r="C9">
+        <f>IF(Refinancing!E7&lt;=0.01,"PASS","BREACH")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
           <t>Overall</t>
         </is>
       </c>
-      <c r="C9">
-        <f>IF(COUNTIF(C5:C8,"FAIL")+COUNTIF(C5:C8,"REVIEW")=0,"PASS","REVIEW")</f>
+      <c r="C10">
+        <f>IF(COUNTIF(C5:C9,"FAIL")+COUNTIF(C5:C9,"BREACH")&gt;0,"FAIL",IF(COUNTIF(C5:C9,"REVIEW")&gt;0,"REVIEW","PASS"))</f>
         <v/>
       </c>
     </row>
@@ -1250,7 +1261,7 @@
   <mergeCells count="1">
     <mergeCell ref="B2:C2"/>
   </mergeCells>
-  <conditionalFormatting sqref="C5:C9">
+  <conditionalFormatting sqref="C5:C10">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>C5="PASS"</formula>
     </cfRule>
@@ -4500,7 +4511,7 @@
         </is>
       </c>
       <c r="E5" s="15">
-        <f>SUM(C5:C7)</f>
+        <f>MIN(MAX(0,C8-E6),Assumptions!E18*Assumptions!E5)</f>
         <v/>
       </c>
       <c r="F5" s="20">
@@ -4524,7 +4535,7 @@
         </is>
       </c>
       <c r="E6" s="15">
-        <f>MAX(0,Assumptions!E6-Assumptions!E17)</f>
+        <f>MIN(MAX(0,Assumptions!E6-Assumptions!E17),C8)</f>
         <v/>
       </c>
     </row>
